--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>29,6</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30,3</t>
+          <t>37,1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -508,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35,3</t>
+          <t>36,2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>34,5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>27,5</t>
+          <t>29,6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -574,12 +574,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>28,8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>31,7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>27,4</t>
+          <t>29,2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>33,6</t>
+          <t>34,9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>37,4</t>
+          <t>33,1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>29,1</t>
+          <t>31,5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26,3</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>28,9</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>35,2</t>
+          <t>32,5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30,8</t>
+          <t>30,4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>27,5</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>33,4</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>28,6</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>31,7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>28,8</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>33,2</t>
+          <t>35,5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32,5</t>
+          <t>32,6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>32,5</t>
+          <t>34,6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>33,4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>27,9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>37,7</t>
+          <t>37,9</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>27,3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>27,1</t>
+          <t>27,2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>31,9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>37,1</t>
+          <t>40,7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36,2</t>
+          <t>36,6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>34,5</t>
+          <t>30,6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29,6</t>
+          <t>25,6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28,8</t>
+          <t>23,7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>31,7</t>
+          <t>29,8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>28,8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>29,2</t>
+          <t>21,6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>34,9</t>
+          <t>34,8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>31,5</t>
+          <t>25,5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>17,3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -750,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25,5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>32,5</t>
+          <t>32,6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30,4</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>27,2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>35,6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>24,4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>31,7</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>31,5</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>35,5</t>
+          <t>34,5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32,6</t>
+          <t>32,9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>34,6</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>33,4</t>
+          <t>27,4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>27,9</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>37,9</t>
+          <t>34,8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>27,3</t>
+          <t>26,3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>27,2</t>
+          <t>21,3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>31,9</t>
+          <t>27,9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -444,15 +444,19 @@
           <t>ADANA</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HATA</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -464,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23,8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -486,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40,7</t>
+          <t>31,9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -508,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36,6</t>
+          <t>34,9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -518,7 +522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -530,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30,6</t>
+          <t>28,3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -552,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,6</t>
+          <t>24,1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -574,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>23,7</t>
+          <t>24,3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -596,12 +600,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29,8</t>
+          <t>29,1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -618,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>28,8</t>
+          <t>27,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -628,7 +632,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -640,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21,6</t>
+          <t>20,8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -662,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>34,8</t>
+          <t>32,1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -684,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>33,1</t>
+          <t>32,2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -706,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25,5</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -728,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17,3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -750,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>25,5</t>
+          <t>24,9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -772,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>32,6</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -794,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>33,5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -804,7 +808,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -816,17 +820,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>27,2</t>
+          <t>25,8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -838,12 +842,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>35,6</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -860,17 +864,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>24,4</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -882,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>23,3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -904,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -914,7 +918,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -926,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -936,7 +940,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -948,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>23,5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -970,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>34,5</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -992,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32,9</t>
+          <t>31,7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1002,7 +1006,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>33,4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1040,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27,4</t>
+          <t>26,8</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24,4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1068,7 +1072,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>34,8</t>
+          <t>31,5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1090,7 +1094,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>26,3</t>
+          <t>26,6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1128,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21,3</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>27,9</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -444,19 +444,15 @@
           <t>ADANA</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -468,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>23,8</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -490,7 +486,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31,9</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -512,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34,9</t>
+          <t>34,8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -534,12 +530,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>28,3</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -556,12 +552,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24,1</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -578,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24,3</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -600,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29,1</t>
+          <t>30,3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -622,7 +618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>27,1</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -632,7 +628,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -644,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20,8</t>
+          <t>24,6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -666,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>32,1</t>
+          <t>34,1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -688,12 +684,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>32,2</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -710,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -732,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21,4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -754,7 +750,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24,9</t>
+          <t>28,3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -776,7 +772,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33,5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -786,7 +782,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -798,7 +794,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>33,5</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,7 +816,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>25,8</t>
+          <t>27,5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -830,7 +826,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -842,12 +838,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>29,1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -864,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>25,6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -886,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>23,3</t>
+          <t>25,7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -908,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -930,12 +926,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -952,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>23,5</t>
+          <t>26,9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -974,12 +970,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33,2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -996,12 +992,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31,7</t>
+          <t>32,6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1018,12 +1014,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>33,4</t>
+          <t>31,3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1040,7 +1036,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>26,8</t>
+          <t>28,5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1050,7 +1046,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1058,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>24,4</t>
+          <t>23,4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1084,12 +1080,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>31,5</t>
+          <t>32,5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1106,12 +1102,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>26,6</t>
+          <t>26,1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1128,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>24,4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1146,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>29,2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>29,5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -508,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34,8</t>
+          <t>35,2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>29,8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30,3</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>28,9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24,6</t>
+          <t>26,9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>34,1</t>
+          <t>35,5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35,3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>24,2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>28,3</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>33,5</t>
+          <t>33,8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>27,5</t>
+          <t>28,4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>29,1</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>25,6</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>25,7</t>
+          <t>29,2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>29,1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>26,9</t>
+          <t>29,8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>33,2</t>
+          <t>34,2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32,6</t>
+          <t>31,7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>31,3</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>28,5</t>
+          <t>32,1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>23,4</t>
+          <t>24,5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>32,5</t>
+          <t>34,4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>26,1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24,4</t>
+          <t>24,9</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,7 +447,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>29,2</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29,5</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35,2</t>
+          <t>35,9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>33,1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>29,4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>29,8</t>
+          <t>27,9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>28,9</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26,9</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>35,5</t>
+          <t>36,4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -684,12 +684,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>35,3</t>
+          <t>36,3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>29,5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24,2</t>
+          <t>26,1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -750,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>31,7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>28,4</t>
+          <t>28,5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>31,7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>29,2</t>
+          <t>31,3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>29,1</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>29,8</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31,7</t>
+          <t>31,9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35,2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>32,1</t>
+          <t>30,3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>24,5</t>
+          <t>24,7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>34,4</t>
+          <t>35,6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>25,4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24,9</t>
+          <t>24,6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>31,1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -513,12 +513,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>33,1</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>29,2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>27,9</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>31,1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>30,3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>36,4</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>36,3</t>
+          <t>37,6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>29,5</t>
+          <t>28,9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26,1</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>31,7</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>33,8</t>
+          <t>33,7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>28,5</t>
+          <t>26,1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>31,7</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>31,3</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>34,2</t>
+          <t>33,6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31,9</t>
+          <t>31,7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>35,2</t>
+          <t>35,6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30,3</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>24,7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>35,6</t>
+          <t>37,9</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>25,4</t>
+          <t>24,5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24,6</t>
+          <t>25,7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>31,9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>31,1</t>
+          <t>33,4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -484,19 +484,15 @@
           <t>ANTALYA</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>29,9</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -508,17 +504,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35,9</t>
+          <t>34,2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -530,17 +526,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -552,17 +548,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29,2</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -574,17 +570,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -596,17 +592,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>31,1</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -618,7 +614,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>24,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -628,7 +624,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -640,17 +636,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30,3</t>
+          <t>33,2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -662,17 +658,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>36,5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -684,12 +680,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>37,6</t>
+          <t>37,2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -706,17 +702,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>28,9</t>
+          <t>27,4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -728,17 +724,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>27,3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -750,12 +746,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>32,3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -772,17 +768,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>33,7</t>
+          <t>33,5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -794,7 +790,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>30,1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -804,7 +800,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -816,7 +812,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>26,1</t>
+          <t>23,6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -826,7 +822,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -838,12 +834,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -865,12 +861,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -882,17 +878,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>34,8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -904,7 +900,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>16,6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -926,17 +922,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -948,7 +944,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33,2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -958,7 +954,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -970,12 +966,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>33,6</t>
+          <t>32,1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -992,12 +988,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31,7</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1014,12 +1010,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>35,6</t>
+          <t>32,9</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1036,17 +1032,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1054,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>25,5</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1076,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>37,9</t>
+          <t>35,7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1098,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>24,5</t>
+          <t>20,4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1120,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>25,7</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1142,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>31,9</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -444,15 +444,19 @@
           <t>ADANA</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HATA</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -464,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>33,4</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -484,15 +488,19 @@
           <t>ANTALYA</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HATA</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -504,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34,2</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -526,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -548,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -570,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -592,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -614,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24,1</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -636,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>33,2</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -658,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>36,5</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -680,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>37,2</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -702,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>27,4</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -724,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>27,3</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -746,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>32,3</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -768,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>33,5</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -790,17 +798,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30,1</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -812,17 +820,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>23,6</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -834,17 +842,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -856,17 +864,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -878,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>34,8</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -900,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16,6</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -922,17 +930,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -944,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>33,2</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -966,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>32,1</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -988,17 +996,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1010,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>32,9</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1040,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1062,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>25,5</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1084,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>35,7</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20,4</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1120,17 +1128,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -444,19 +444,15 @@
           <t>ADANA</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -468,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25,3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -490,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>29,2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -512,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30,8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -534,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -556,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>22,7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -578,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>21,7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -600,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25,2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -622,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24,8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -644,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26,6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -666,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -688,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>36,5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -710,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23,1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -732,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>27,2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -754,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -776,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32,3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -798,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30,4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -820,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -842,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -864,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>28,3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -886,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26,8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -908,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24,9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -930,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -952,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -974,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -996,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>31,9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>29,6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24,8</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>22,4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1084,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33,3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -1106,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24,1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23,4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1150,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>21</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25,3</t>
+          <t>24,9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29,2</t>
+          <t>28,9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -508,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30,8</t>
+          <t>29,5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -530,12 +530,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>21,8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22,7</t>
+          <t>17,2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>16,4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,2</t>
+          <t>18,5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>22,7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26,6</t>
+          <t>21,8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>25,5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>36,5</t>
+          <t>35,8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>23,1</t>
+          <t>18,4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>27,2</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20,2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>32,3</t>
+          <t>32,8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30,4</t>
+          <t>31,2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>18,9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>28,3</t>
+          <t>30,3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>26,8</t>
+          <t>24,4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>24,9</t>
+          <t>23,7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>19,1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>29,1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31,9</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>29,6</t>
+          <t>25,5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>18,4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>22,4</t>
+          <t>19,2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>33,3</t>
+          <t>34,6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>24,1</t>
+          <t>21,9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>23,4</t>
+          <t>21,9</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>18,2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -464,12 +464,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24,9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>28,9</t>
+          <t>24,8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -508,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29,5</t>
+          <t>25,7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21,8</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17,2</t>
+          <t>21,1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>15,4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18,5</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22,7</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21,8</t>
+          <t>21,3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>25,5</t>
+          <t>23,2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>35,8</t>
+          <t>35,6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18,4</t>
+          <t>19,5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -750,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20,2</t>
+          <t>15,4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>32,8</t>
+          <t>32,4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>31,5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18,9</t>
+          <t>23,9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>30,3</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>24,4</t>
+          <t>20,2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>23,7</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19,1</t>
+          <t>23,4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>29,1</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>29,1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>25,5</t>
+          <t>22,3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18,4</t>
+          <t>21,2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19,2</t>
+          <t>21,3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>34,6</t>
+          <t>32,9</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21,9</t>
+          <t>23,2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21,9</t>
+          <t>22,9</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18,2</t>
+          <t>21,8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>31,1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -508,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25,7</t>
+          <t>30,4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>25,3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21,1</t>
+          <t>21,3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -574,12 +574,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15,4</t>
+          <t>19,9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -618,12 +618,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21,3</t>
+          <t>24,8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23,2</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>35,6</t>
+          <t>34,8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19,5</t>
+          <t>23,3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15,4</t>
+          <t>20,7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>32,4</t>
+          <t>26,1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31,5</t>
+          <t>26,9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>23,9</t>
+          <t>24,3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>24,4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20,2</t>
+          <t>23,6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>23,4</t>
+          <t>21,6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>22,8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -970,12 +970,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>29,1</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>28,6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>22,3</t>
+          <t>27,2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21,2</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21,3</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>32,9</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>23,2</t>
+          <t>24,2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>22,9</t>
+          <t>23,4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21,8</t>
+          <t>22,4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -444,15 +444,19 @@
           <t>ADANA</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HATA</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -464,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -486,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31,1</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -508,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30,4</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -530,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,3</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -552,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21,3</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -574,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19,9</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -596,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -618,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -640,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -662,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -684,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>34,8</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -706,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>23,3</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -728,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -750,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -772,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>26,1</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -794,17 +798,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>26,9</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -816,17 +820,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>24,3</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -838,17 +842,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -860,17 +864,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>24,4</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -882,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>23,6</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -904,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -926,17 +930,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21,6</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -948,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>22,8</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -970,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -992,17 +996,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>28,6</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>27,2</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1040,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1062,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1084,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>24,2</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1128,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>23,4</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>22,4</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>HATA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>HATA</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -444,19 +444,15 @@
           <t>ADANA</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -468,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -490,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>29,4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -512,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32,3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -534,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -556,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23,4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -578,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>21,2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -600,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26,6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -622,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -644,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25,3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -666,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>29,5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -688,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33,5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -710,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24,3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -732,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>21,9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -754,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -776,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>31,5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -798,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>29,2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -820,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -842,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>27,9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -864,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25,2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -886,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25,7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -908,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>27,2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -930,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>27,3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -952,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24,7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -974,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -996,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>30,4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26,3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1084,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>33,3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -1106,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24,3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>24,2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1150,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>27,4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>HATA</t>
+          <t>26</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -508,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32,3</t>
+          <t>33,1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>29,7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>23,4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21,2</t>
+          <t>22,2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,6</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>29,9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>25,3</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>29,5</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>33,5</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>24,3</t>
+          <t>24,2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21,9</t>
+          <t>20,7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -750,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>24,7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>31,5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>29,2</t>
+          <t>28,9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>24,4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>27,9</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>25,2</t>
+          <t>25,6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>25,7</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>27,2</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>27,3</t>
+          <t>27,9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>24,7</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>31,6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>30,4</t>
+          <t>29,3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>26,3</t>
+          <t>26,5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>33,3</t>
+          <t>30,9</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>24,3</t>
+          <t>24,4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24,2</t>
+          <t>22,7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>27,4</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>24,4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>26,6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -508,12 +508,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33,1</t>
+          <t>32,6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29,7</t>
+          <t>21,4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19,9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22,2</t>
+          <t>21,3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>29,9</t>
+          <t>19,2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>29,4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34,8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>24,2</t>
+          <t>22,7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>23,7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24,7</t>
+          <t>23,5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31,9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>28,9</t>
+          <t>29,8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>24,4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>25,5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>25,6</t>
+          <t>27,2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>18,8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>27,9</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>26,5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>31,6</t>
+          <t>26,3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>29,6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>26,5</t>
+          <t>21,5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>23,9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30,9</t>
+          <t>33,3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>24,4</t>
+          <t>16,7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>22,7</t>
+          <t>24,4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>24,6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24,4</t>
+          <t>19,1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26,6</t>
+          <t>28,5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -508,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32,6</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>18,7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19,9</t>
+          <t>13,9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21,3</t>
+          <t>14,3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>14,4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19,2</t>
+          <t>21,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>22,9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>25,7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>34,8</t>
+          <t>32,5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22,7</t>
+          <t>16,4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23,7</t>
+          <t>24,9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -750,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>23,5</t>
+          <t>15,1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>31,9</t>
+          <t>27,3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>29,8</t>
+          <t>28,6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16,4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>25,5</t>
+          <t>21,8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>27,2</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20,9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18,8</t>
+          <t>18,3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>15,5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>26,5</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>26,3</t>
+          <t>21,2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>29,6</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21,5</t>
+          <t>17,1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>23,9</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>33,3</t>
+          <t>30,8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16,7</t>
+          <t>21,1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24,4</t>
+          <t>25,3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>24,6</t>
+          <t>14,7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19,1</t>
+          <t>18,5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>28,5</t>
+          <t>27,4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -508,12 +508,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>26,1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18,7</t>
+          <t>22,9</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13,9</t>
+          <t>17,2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14,3</t>
+          <t>15,8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14,4</t>
+          <t>20,5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -618,12 +618,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21,1</t>
+          <t>22,6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22,9</t>
+          <t>15,9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -662,12 +662,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>25,7</t>
+          <t>24,4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -684,12 +684,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>32,5</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>19,8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24,9</t>
+          <t>21,7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -750,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15,1</t>
+          <t>17,6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>27,3</t>
+          <t>26,1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>28,6</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>20,5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21,8</t>
+          <t>25,3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>16,1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18,3</t>
+          <t>21,6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15,5</t>
+          <t>21,7</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>16,2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21,2</t>
+          <t>24,9</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>29,5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17,1</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30,8</t>
+          <t>29,7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21,1</t>
+          <t>20,7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>25,3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14,7</t>
+          <t>18,6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18,5</t>
+          <t>20,1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27,4</t>
+          <t>26,3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -508,12 +508,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26,1</t>
+          <t>29,1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22,9</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17,2</t>
+          <t>21,1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15,8</t>
+          <t>21,8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20,5</t>
+          <t>24,6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22,6</t>
+          <t>22,7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -640,12 +640,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15,9</t>
+          <t>16,6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24,4</t>
+          <t>26,8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>31,3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19,8</t>
+          <t>23,9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>23,3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -750,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17,6</t>
+          <t>22,2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>26,1</t>
+          <t>28,8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>29,3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20,5</t>
+          <t>22,1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>25,3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16,1</t>
+          <t>23,4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20,9</t>
+          <t>19,3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>24,7</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16,2</t>
+          <t>21,5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>24,9</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>29,5</t>
+          <t>30,3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>24,8</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>23,8</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>18,8</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>29,7</t>
+          <t>30,4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>21,4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21,4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18,6</t>
+          <t>22,3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20,1</t>
+          <t>22,2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26,3</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -508,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29,1</t>
+          <t>28,8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21,1</t>
+          <t>22,8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21,8</t>
+          <t>22,2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24,6</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -618,12 +618,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22,7</t>
+          <t>24,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16,6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>26,8</t>
+          <t>26,6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>31,3</t>
+          <t>34,6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>23,9</t>
+          <t>22,7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23,3</t>
+          <t>25,2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22,2</t>
+          <t>22,4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -770,19 +770,15 @@
           <t>GAZİANTEP</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>28,8</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -794,17 +790,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>29,3</t>
+          <t>29,4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -816,17 +812,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22,1</t>
+          <t>25,2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -838,12 +834,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26,3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -860,7 +856,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>23,4</t>
+          <t>24,5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -870,7 +866,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -882,17 +878,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19,3</t>
+          <t>23,5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -904,7 +900,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21,6</t>
+          <t>20,8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -914,7 +910,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -926,7 +922,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>24,7</t>
+          <t>24,6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -936,7 +932,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -948,17 +944,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21,5</t>
+          <t>23,6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -970,7 +966,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -980,7 +976,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -992,17 +988,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>30,3</t>
+          <t>30,7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1010,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>24,7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1032,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>23,8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1054,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18,8</t>
+          <t>21,8</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1080,17 +1076,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30,4</t>
+          <t>33,3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1098,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>23,4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1124,7 +1120,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>21,3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1134,7 +1130,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1142,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>22,3</t>
+          <t>23,2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22,2</t>
+          <t>23,7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>23,9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28,8</t>
+          <t>19,6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>22,6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22,8</t>
+          <t>18,1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -574,12 +574,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22,2</t>
+          <t>18,2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24,1</t>
+          <t>23,6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>26,6</t>
+          <t>18,9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>34,6</t>
+          <t>35,2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22,7</t>
+          <t>20,7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>25,2</t>
+          <t>21,1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22,4</t>
+          <t>18,5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -812,17 +812,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>25,2</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>26,3</t>
+          <t>19,2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>24,5</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -878,17 +878,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>23,5</t>
+          <t>23,1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -900,17 +900,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20,8</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>24,6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -944,12 +944,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>23,6</t>
+          <t>23,9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -966,17 +966,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>18,1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -988,17 +988,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>30,7</t>
+          <t>29,2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1010,17 +1010,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>24,7</t>
+          <t>15,3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21,8</t>
+          <t>21,6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>33,3</t>
+          <t>34,2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>23,4</t>
+          <t>19,9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21,3</t>
+          <t>21,7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1142,17 +1142,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>23,2</t>
+          <t>17,9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -464,12 +464,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>23,7</t>
+          <t>15,1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>23,9</t>
+          <t>26,6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19,6</t>
+          <t>24,7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22,6</t>
+          <t>20,7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18,1</t>
+          <t>13,7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18,2</t>
+          <t>14,6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18,1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>23,6</t>
+          <t>24,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18,9</t>
+          <t>20,2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>35,2</t>
+          <t>25,8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>17,7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21,1</t>
+          <t>18,5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18,5</t>
+          <t>13,7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -770,15 +770,19 @@
           <t>GAZİANTEP</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>18,2</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -790,7 +794,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24,1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -812,7 +816,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>19,2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -822,7 +826,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -834,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19,2</t>
+          <t>23,6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -844,7 +848,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -856,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13,1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -878,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>23,1</t>
+          <t>17,9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -900,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -922,7 +926,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17,3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -932,7 +936,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -944,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>23,9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -966,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18,1</t>
+          <t>22,8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -988,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>29,2</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1010,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15,3</t>
+          <t>20,7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1036,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>17,6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1042,7 +1046,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21,6</t>
+          <t>19,7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1080,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>34,2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1098,7 +1102,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19,9</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1108,7 +1112,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1124,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>20,5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1142,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17,9</t>
+          <t>14,5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15,1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26,6</t>
+          <t>26,5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24,7</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>17,3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13,7</t>
+          <t>16,4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18,1</t>
+          <t>16,9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24,1</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -640,12 +640,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18,9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20,2</t>
+          <t>22,3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>25,8</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17,7</t>
+          <t>16,5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18,5</t>
+          <t>14,6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13,7</t>
+          <t>15,1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18,2</t>
+          <t>23,3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24,1</t>
+          <t>26,1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19,2</t>
+          <t>17,5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>23,6</t>
+          <t>22,9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13,1</t>
+          <t>18,2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17,9</t>
+          <t>18,5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16,5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17,3</t>
+          <t>17,7</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19,2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>22,8</t>
+          <t>20,6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28,3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>24,7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17,6</t>
+          <t>18,1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19,7</t>
+          <t>19,8</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18,9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20,5</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14,5</t>
+          <t>16,3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,7 +447,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -464,12 +464,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16,2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26,5</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17,3</t>
+          <t>18,9</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -552,12 +552,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>15,4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14,6</t>
+          <t>13,1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16,9</t>
+          <t>19,2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>21,8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18,9</t>
+          <t>14,9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22,3</t>
+          <t>24,4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>26,9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -706,12 +706,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16,5</t>
+          <t>18,8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14,6</t>
+          <t>17,1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -750,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15,1</t>
+          <t>15,8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>23,3</t>
+          <t>25,2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>26,1</t>
+          <t>25,6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17,5</t>
+          <t>20,9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22,9</t>
+          <t>24,7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18,2</t>
+          <t>19,2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18,5</t>
+          <t>17,4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16,5</t>
+          <t>19,6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17,7</t>
+          <t>19,1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19,2</t>
+          <t>20,1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20,6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>28,3</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>24,7</t>
+          <t>16,8</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18,1</t>
+          <t>19,6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19,8</t>
+          <t>20,2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18,9</t>
+          <t>21,3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>19,7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16,3</t>
+          <t>21,5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16,2</t>
+          <t>17,3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -486,12 +486,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>27,3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -530,12 +530,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18,9</t>
+          <t>20,2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15,4</t>
+          <t>16,4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -574,12 +574,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13,1</t>
+          <t>14,4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19,2</t>
+          <t>18,3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14,9</t>
+          <t>14,6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -662,12 +662,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24,4</t>
+          <t>20,7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>26,9</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18,8</t>
+          <t>17,3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17,1</t>
+          <t>9,4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15,8</t>
+          <t>16,7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>25,2</t>
+          <t>16,5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>25,6</t>
+          <t>23,3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20,9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>24,7</t>
+          <t>23,3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19,2</t>
+          <t>15,8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17,4</t>
+          <t>16,4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19,6</t>
+          <t>17,6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19,1</t>
+          <t>18,5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20,1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>18,5</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16,8</t>
+          <t>20,2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19,6</t>
+          <t>18,7</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20,2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>24,3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21,3</t>
+          <t>18,6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19,7</t>
+          <t>16,7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21,5</t>
+          <t>16,7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17,3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>23,6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27,3</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20,2</t>
+          <t>19,7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>15,3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14,4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18,3</t>
+          <t>16,4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21,8</t>
+          <t>16,7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14,6</t>
+          <t>16,3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>21,1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15,3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -728,12 +728,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9,4</t>
+          <t>12,5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -750,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16,7</t>
+          <t>16,2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16,5</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>23,3</t>
+          <t>20,2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>23,3</t>
+          <t>23,9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15,8</t>
+          <t>13,8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>14,8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17,6</t>
+          <t>19,3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18,5</t>
+          <t>17,4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12,8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18,5</t>
+          <t>23,2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>23,6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18,7</t>
+          <t>18,5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16,3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>24,3</t>
+          <t>23,3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18,6</t>
+          <t>20,7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16,7</t>
+          <t>18,8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16,7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>17,8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -486,12 +486,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>23,6</t>
+          <t>21,3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -508,12 +508,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -530,12 +530,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19,7</t>
+          <t>21,1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15,3</t>
+          <t>17,3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17,5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>19,8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -618,12 +618,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16,7</t>
+          <t>21,6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16,3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21,1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15,3</t>
+          <t>19,3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17,3</t>
+          <t>19,1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12,5</t>
+          <t>11,8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16,2</t>
+          <t>19,6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20,2</t>
+          <t>25,2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>20,9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>23,9</t>
+          <t>24,4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13,8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14,8</t>
+          <t>17,7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17,4</t>
+          <t>20,7</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12,8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>23,2</t>
+          <t>23,4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>23,6</t>
+          <t>27,1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20,2</t>
+          <t>18,8</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18,5</t>
+          <t>19,9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16,3</t>
+          <t>19,3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>23,3</t>
+          <t>25,2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>20,2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18,8</t>
+          <t>19,3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16,3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -464,12 +464,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17,8</t>
+          <t>19,5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21,3</t>
+          <t>24,5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -508,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>28,3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21,1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -552,12 +552,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17,3</t>
+          <t>18,7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17,5</t>
+          <t>18,2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19,8</t>
+          <t>21,7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21,6</t>
+          <t>22,8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23,4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -684,12 +684,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19,3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19,1</t>
+          <t>19,7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11,8</t>
+          <t>16,5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19,6</t>
+          <t>20,1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22,2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>25,2</t>
+          <t>27,2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20,9</t>
+          <t>20,5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>24,4</t>
+          <t>26,6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19,4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17,7</t>
+          <t>19,9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19,3</t>
+          <t>20,9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>21,4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16,7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>23,4</t>
+          <t>24,4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>27,1</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>18,8</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19,9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19,3</t>
+          <t>18,6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>25,2</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20,2</t>
+          <t>20,9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19,3</t>
+          <t>18,5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16,3</t>
+          <t>19,8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,7 +447,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -486,12 +486,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24,5</t>
+          <t>24,1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28,3</t>
+          <t>23,6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20,2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18,7</t>
+          <t>16,1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18,2</t>
+          <t>13,4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>19,3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22,8</t>
+          <t>21,4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>15,9</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23,4</t>
+          <t>18,8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -684,12 +684,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19,2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -706,12 +706,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19,7</t>
+          <t>16,2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16,5</t>
+          <t>8,2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -750,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20,1</t>
+          <t>16,8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22,2</t>
+          <t>18,4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>27,2</t>
+          <t>21,7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20,5</t>
+          <t>18,9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>26,6</t>
+          <t>21,3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19,4</t>
+          <t>13,8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19,9</t>
+          <t>19,8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20,9</t>
+          <t>20,5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>18,4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16,7</t>
+          <t>17,6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>24,4</t>
+          <t>24,1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>25,5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18,6</t>
+          <t>18,5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>22,2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20,9</t>
+          <t>20,4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18,5</t>
+          <t>18,1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19,8</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19,5</t>
+          <t>20,6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24,1</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -508,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23,6</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20,2</t>
+          <t>22,4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -552,12 +552,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16,1</t>
+          <t>19,1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13,4</t>
+          <t>15,7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19,3</t>
+          <t>21,8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15,9</t>
+          <t>15,7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18,8</t>
+          <t>26,6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19,2</t>
+          <t>21,2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16,2</t>
+          <t>18,6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8,2</t>
+          <t>9,2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -750,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16,8</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18,4</t>
+          <t>18,9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>24,2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18,9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21,3</t>
+          <t>23,1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13,8</t>
+          <t>17,1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19,8</t>
+          <t>20,9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20,5</t>
+          <t>23,2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18,4</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17,6</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>24,1</t>
+          <t>25,8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>25,5</t>
+          <t>24,8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>24,7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20,8</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18,5</t>
+          <t>16,7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>22,2</t>
+          <t>22,4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20,4</t>
+          <t>20,6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18,1</t>
+          <t>16,2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>22,3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20,6</t>
+          <t>19,6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>24,8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -508,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22,4</t>
+          <t>22,2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19,1</t>
+          <t>19,4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15,7</t>
+          <t>18,3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21,8</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>22,9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15,7</t>
+          <t>18,9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>26,6</t>
+          <t>24,9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21,2</t>
+          <t>23,1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18,6</t>
+          <t>19,4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9,2</t>
+          <t>8,6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -750,17 +750,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21,4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18,9</t>
+          <t>20,5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24,2</t>
+          <t>24,6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>21,4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>23,1</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17,1</t>
+          <t>18,3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20,9</t>
+          <t>21,1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>23,2</t>
+          <t>24,4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20,7</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20,1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>26,1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>24,7</t>
+          <t>22,6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20,8</t>
+          <t>20,1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16,7</t>
+          <t>18,7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>22,4</t>
+          <t>23,1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20,6</t>
+          <t>20,5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16,2</t>
+          <t>18,8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>22,3</t>
+          <t>21,9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19,6</t>
+          <t>20,9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>24,6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -508,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25,5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -530,12 +530,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22,2</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19,4</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18,3</t>
+          <t>19,6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>22,6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22,9</t>
+          <t>20,4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18,9</t>
+          <t>20,1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24,9</t>
+          <t>25,2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23,1</t>
+          <t>23,7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19,4</t>
+          <t>22,2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8,6</t>
+          <t>14,5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>21,6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20,5</t>
+          <t>22,3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24,6</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>19,3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>23,6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18,3</t>
+          <t>19,5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21,1</t>
+          <t>20,9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>24,4</t>
+          <t>23,6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20,1</t>
+          <t>21,2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>25,8</t>
+          <t>25,6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>26,1</t>
+          <t>27,2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>22,6</t>
+          <t>21,7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20,1</t>
+          <t>23,1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18,7</t>
+          <t>20,7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>23,1</t>
+          <t>25,2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20,5</t>
+          <t>20,1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18,8</t>
+          <t>19,8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21,9</t>
+          <t>21,2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,7 +447,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20,9</t>
+          <t>22,2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24,6</t>
+          <t>26,1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -508,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25,5</t>
+          <t>29,1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29,2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19,6</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22,6</t>
+          <t>25,7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20,4</t>
+          <t>21,7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20,1</t>
+          <t>22,6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>25,2</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23,7</t>
+          <t>22,4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22,2</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14,5</t>
+          <t>11,1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21,6</t>
+          <t>24,2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22,3</t>
+          <t>22,8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28,9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19,3</t>
+          <t>22,1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>23,6</t>
+          <t>24,2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19,5</t>
+          <t>21,4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20,9</t>
+          <t>25,2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>23,6</t>
+          <t>26,6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24,8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21,2</t>
+          <t>22,3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>25,6</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>27,2</t>
+          <t>28,6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>24,6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>23,1</t>
+          <t>27,1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>20,6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>25,2</t>
+          <t>25,4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20,1</t>
+          <t>21,7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19,8</t>
+          <t>18,5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21,2</t>
+          <t>23,7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22,2</t>
+          <t>24,3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26,1</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -508,17 +508,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29,1</t>
+          <t>31,1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29,2</t>
+          <t>31,4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>25,8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25,7</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>24,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -640,12 +640,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22,6</t>
+          <t>25,2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29,1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22,4</t>
+          <t>25,4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>27,4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11,1</t>
+          <t>17,5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24,2</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22,8</t>
+          <t>25,7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>28,9</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22,1</t>
+          <t>22,9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>24,2</t>
+          <t>28,3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>24,3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>25,2</t>
+          <t>24,8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>26,6</t>
+          <t>26,9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>28,5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>22,3</t>
+          <t>23,3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>28,6</t>
+          <t>30,2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>24,6</t>
+          <t>24,8</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27,1</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20,6</t>
+          <t>22,2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>25,4</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>21,3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18,5</t>
+          <t>21,7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>23,7</t>
+          <t>25,6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -447,12 +447,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -464,17 +464,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24,3</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>27,4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31,1</t>
+          <t>28,2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>31,4</t>
+          <t>29,5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -552,17 +552,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25,8</t>
+          <t>27,5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>25,2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>29,4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24,1</t>
+          <t>22,9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -640,17 +640,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>25,2</t>
+          <t>26,3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -662,17 +662,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>29,1</t>
+          <t>28,7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>25,4</t>
+          <t>25,2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -706,17 +706,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>27,4</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17,5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>25,4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>25,7</t>
+          <t>24,6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>28,9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22,9</t>
+          <t>23,8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>28,3</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>24,3</t>
+          <t>22,4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>26,5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>26,9</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>28,5</t>
+          <t>27,3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>23,3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>28,8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>30,2</t>
+          <t>29,1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>23,6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27,9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>22,2</t>
+          <t>21,8</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>26,3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21,3</t>
+          <t>21,4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>25,6</t>
+          <t>24,6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -444,15 +444,19 @@
           <t>ADANA</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>23,7</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -464,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>16,2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -474,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -486,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27,4</t>
+          <t>24,5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -496,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -508,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>23,3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -518,7 +522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -530,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29,5</t>
+          <t>22,3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -552,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>27,5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -574,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25,2</t>
+          <t>18,6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -584,7 +588,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -596,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29,4</t>
+          <t>21,4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -618,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22,9</t>
+          <t>19,9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -640,12 +644,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26,3</t>
+          <t>15,3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -662,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>28,7</t>
+          <t>20,9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -672,7 +676,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -684,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>25,2</t>
+          <t>19,5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -706,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -716,7 +720,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -728,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>9,1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
     </row>
@@ -750,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>25,4</t>
+          <t>16,2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -772,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24,6</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -794,17 +798,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>28,9</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -816,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>23,8</t>
+          <t>20,9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -826,7 +830,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -838,17 +842,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>21,8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -860,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22,4</t>
+          <t>19,5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -870,7 +874,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -882,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>26,5</t>
+          <t>19,7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -892,7 +896,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -904,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>15,9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -926,17 +930,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>27,3</t>
+          <t>21,1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -948,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18,7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -970,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>28,8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -992,12 +996,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>29,1</t>
+          <t>22,9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1014,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>23,6</t>
+          <t>17,7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1040,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27,9</t>
+          <t>20,9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1062,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21,8</t>
+          <t>23,5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1084,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>26,3</t>
+          <t>23,6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1128,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>24,1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1146,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>24,6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23,7</t>
+          <t>25,7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16,2</t>
+          <t>19,9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24,5</t>
+          <t>23,2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23,3</t>
+          <t>24,1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22,3</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17,3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18,6</t>
+          <t>17,5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>17,7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19,9</t>
+          <t>15,4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15,3</t>
+          <t>20,1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20,9</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19,5</t>
+          <t>19,8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -710,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>18,3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9,1</t>
+          <t>10,2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16,2</t>
+          <t>18,7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18,7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24,7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -820,17 +820,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20,9</t>
+          <t>16,5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -842,17 +842,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21,8</t>
+          <t>23,5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19,5</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19,7</t>
+          <t>21,8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15,9</t>
+          <t>12,2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21,1</t>
+          <t>18,9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18,7</t>
+          <t>19,6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21,1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22,9</t>
+          <t>25,5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17,7</t>
+          <t>15,3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1040,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20,9</t>
+          <t>19,5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1062,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>23,5</t>
+          <t>20,7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>23,6</t>
+          <t>23,4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14,1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24,1</t>
+          <t>23,2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17,6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25,7</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19,9</t>
+          <t>15,9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>23,2</t>
+          <t>18,8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24,1</t>
+          <t>17,6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -534,12 +534,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18,2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17,3</t>
+          <t>17,2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17,5</t>
+          <t>17,7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17,7</t>
+          <t>20,5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15,4</t>
+          <t>12,4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20,1</t>
+          <t>16,4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>20,7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19,8</t>
+          <t>23,4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -710,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18,3</t>
+          <t>18,4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10,2</t>
+          <t>15,2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18,7</t>
+          <t>15,1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18,7</t>
+          <t>23,5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24,7</t>
+          <t>26,5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,17 +820,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16,5</t>
+          <t>17,2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -842,17 +842,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>23,5</t>
+          <t>20,7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -864,17 +864,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -886,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21,8</t>
+          <t>17,2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12,2</t>
+          <t>10,7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18,9</t>
+          <t>20,5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19,6</t>
+          <t>13,2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21,1</t>
+          <t>19,7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>25,5</t>
+          <t>27,5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15,3</t>
+          <t>11,6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1040,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19,5</t>
+          <t>20,6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1062,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>23,4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1106,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14,1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1128,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>23,2</t>
+          <t>23,3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17,6</t>
+          <t>16,1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15,9</t>
+          <t>18,3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18,8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17,6</t>
+          <t>21,7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18,2</t>
+          <t>13,8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17,2</t>
+          <t>12,6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17,7</t>
+          <t>15,6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20,5</t>
+          <t>13,4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12,4</t>
+          <t>18,3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>16,2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23,4</t>
+          <t>24,5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -710,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18,4</t>
+          <t>16,1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15,2</t>
+          <t>14,2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15,1</t>
+          <t>13,1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>23,5</t>
+          <t>20,9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>26,5</t>
+          <t>22,4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17,2</t>
+          <t>13,3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -842,17 +842,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>18,5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -864,17 +864,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>18,6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -886,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17,2</t>
+          <t>18,2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -908,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10,7</t>
+          <t>16,4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20,5</t>
+          <t>14,8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13,2</t>
+          <t>13,7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19,7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>27,5</t>
+          <t>19,8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11,6</t>
+          <t>19,5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1040,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20,6</t>
+          <t>15,4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1062,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>21,4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27,2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>18,2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>23,3</t>
+          <t>21,1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16,1</t>
+          <t>14,5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>25,3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -468,12 +468,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18,3</t>
+          <t>10,1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>22,2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>20,6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13,8</t>
+          <t>15,4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12,6</t>
+          <t>9,4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15,6</t>
+          <t>7,2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13,4</t>
+          <t>13,2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18,3</t>
+          <t>16,3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16,2</t>
+          <t>13,7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14,9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>24,5</t>
+          <t>23,5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -710,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16,1</t>
+          <t>11,7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14,2</t>
+          <t>12,8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13,1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20,9</t>
+          <t>20,4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -796,19 +796,15 @@
           <t>HATAY</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>22,4</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -820,7 +816,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13,3</t>
+          <t>14,9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -830,7 +826,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -842,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18,5</t>
+          <t>20,7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -864,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18,6</t>
+          <t>17,8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -886,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18,2</t>
+          <t>16,8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -908,7 +904,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>14,3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -918,7 +914,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -930,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14,8</t>
+          <t>13,2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -952,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13,7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -974,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18,4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -996,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19,8</t>
+          <t>23,7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19,5</t>
+          <t>17,4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15,4</t>
+          <t>13,3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>17,8</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1080,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>27,2</t>
+          <t>24,7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1106,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18,2</t>
+          <t>16,4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21,1</t>
+          <t>18,8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1150,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14,5</t>
+          <t>9,9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25,3</t>
+          <t>19,6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10,1</t>
+          <t>9,4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22,2</t>
+          <t>21,8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20,6</t>
+          <t>12,9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15,4</t>
+          <t>12,9</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9,4</t>
+          <t>8,6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7,2</t>
+          <t>7,9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -600,12 +600,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13,2</t>
+          <t>12,1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16,3</t>
+          <t>15,9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13,7</t>
+          <t>11,4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -666,12 +666,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14,9</t>
+          <t>10,1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23,5</t>
+          <t>26,9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -710,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11,7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12,8</t>
+          <t>16,7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8,1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20,4</t>
+          <t>23,2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14,9</t>
+          <t>14,2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>15,7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17,8</t>
+          <t>17,2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16,8</t>
+          <t>11,8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13,2</t>
+          <t>13,6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16,2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18,4</t>
+          <t>13,2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>23,7</t>
+          <t>23,3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17,4</t>
+          <t>8,5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13,3</t>
+          <t>12,9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17,8</t>
+          <t>18,1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>24,7</t>
+          <t>25,3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>15,1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18,8</t>
+          <t>21,2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9,9</t>
+          <t>6,6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19,6</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9,4</t>
+          <t>11,6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -490,12 +490,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21,8</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12,9</t>
+          <t>19,8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12,9</t>
+          <t>15,3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8,6</t>
+          <t>12,6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7,9</t>
+          <t>10,9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12,1</t>
+          <t>13,4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15,9</t>
+          <t>14,6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11,4</t>
+          <t>13,6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10,1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>26,9</t>
+          <t>24,6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -710,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16,2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16,7</t>
+          <t>12,7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8,1</t>
+          <t>12,8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>23,2</t>
+          <t>21,2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14,2</t>
+          <t>15,3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15,7</t>
+          <t>19,8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17,2</t>
+          <t>15,9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11,8</t>
+          <t>14,5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14,3</t>
+          <t>14,4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13,6</t>
+          <t>17,1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16,2</t>
+          <t>15,9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13,2</t>
+          <t>15,9</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>23,3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>8,5</t>
+          <t>17,2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12,9</t>
+          <t>16,7</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18,1</t>
+          <t>21,9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>25,3</t>
+          <t>23,7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15,1</t>
+          <t>14,9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21,2</t>
+          <t>21,8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6,6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>23,2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -468,12 +468,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11,6</t>
+          <t>13,1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>22,7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19,8</t>
+          <t>21,2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -534,12 +534,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15,3</t>
+          <t>21,1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12,6</t>
+          <t>15,8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -578,12 +578,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10,9</t>
+          <t>13,8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13,4</t>
+          <t>17,6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14,6</t>
+          <t>19,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13,6</t>
+          <t>14,7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>17,8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>24,6</t>
+          <t>20,7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16,2</t>
+          <t>17,3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12,7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12,8</t>
+          <t>14,7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21,2</t>
+          <t>18,5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -799,12 +799,12 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15,3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19,8</t>
+          <t>19,7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15,9</t>
+          <t>15,4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14,5</t>
+          <t>16,3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14,4</t>
+          <t>20,4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17,1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15,9</t>
+          <t>15,3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15,9</t>
+          <t>20,5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24,1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17,2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16,7</t>
+          <t>18,1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21,9</t>
+          <t>18,4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>23,7</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14,9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21,8</t>
+          <t>18,7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14,6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23,2</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13,1</t>
+          <t>17,3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22,7</t>
+          <t>24,1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21,2</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21,1</t>
+          <t>23,7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15,8</t>
+          <t>17,9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13,8</t>
+          <t>18,7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17,6</t>
+          <t>22,4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19,1</t>
+          <t>20,4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14,7</t>
+          <t>19,4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17,8</t>
+          <t>21,8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>23,1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -710,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17,3</t>
+          <t>22,1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>16,1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14,7</t>
+          <t>16,9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18,5</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19,7</t>
+          <t>22,8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15,4</t>
+          <t>20,2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16,3</t>
+          <t>18,2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20,4</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23,2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15,3</t>
+          <t>17,7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20,5</t>
+          <t>22,3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>24,1</t>
+          <t>26,3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20,2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18,1</t>
+          <t>23,2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18,4</t>
+          <t>18,6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24,6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>18,3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18,7</t>
+          <t>19,6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14,6</t>
+          <t>19,3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>30,4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17,3</t>
+          <t>19,1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -490,12 +490,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24,1</t>
+          <t>24,9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -512,12 +512,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>26,6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -534,12 +534,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>23,7</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17,9</t>
+          <t>19,7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18,7</t>
+          <t>20,8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22,4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20,4</t>
+          <t>19,9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19,4</t>
+          <t>20,6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21,8</t>
+          <t>23,9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23,1</t>
+          <t>21,1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22,1</t>
+          <t>23,4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16,1</t>
+          <t>15,1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16,9</t>
+          <t>19,2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>21,2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19,8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22,8</t>
+          <t>24,3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20,2</t>
+          <t>19,8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18,2</t>
+          <t>19,6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23,2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>23,2</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17,7</t>
+          <t>18,8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>22,3</t>
+          <t>23,4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>26,3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20,2</t>
+          <t>23,1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>23,2</t>
+          <t>23,9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18,6</t>
+          <t>19,3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>24,6</t>
+          <t>24,8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18,3</t>
+          <t>18,7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19,6</t>
+          <t>19,5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19,3</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30,4</t>
+          <t>30,6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19,1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -490,12 +490,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24,9</t>
+          <t>25,3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26,6</t>
+          <t>27,9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19,7</t>
+          <t>21,8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20,8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23,6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19,9</t>
+          <t>22,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20,6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23,9</t>
+          <t>25,7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21,1</t>
+          <t>23,8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>23,4</t>
+          <t>24,7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15,1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19,2</t>
+          <t>21,5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21,2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19,8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>24,3</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19,8</t>
+          <t>20,4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19,6</t>
+          <t>21,7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>23,2</t>
+          <t>20,4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>28,1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18,8</t>
+          <t>20,1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>23,4</t>
+          <t>24,8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27,8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>23,9</t>
+          <t>27,1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19,3</t>
+          <t>21,3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18,7</t>
+          <t>19,2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19,5</t>
+          <t>19,9</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30,6</t>
+          <t>32,3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22,7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25,3</t>
+          <t>25,7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -512,12 +512,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27,9</t>
+          <t>27,7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>27,1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21,8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>23,8</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
     </row>
@@ -600,12 +600,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>23,6</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22,1</t>
+          <t>16,2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23,5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>25,7</t>
+          <t>26,4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23,8</t>
+          <t>24,2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>24,7</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>15,4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21,5</t>
+          <t>22,4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23,8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>27,6</t>
+          <t>26,5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20,4</t>
+          <t>22,9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>22,6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20,4</t>
+          <t>15,5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>28,1</t>
+          <t>24,6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20,1</t>
+          <t>23,2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>26,2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>27,9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>23,1</t>
+          <t>22,1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27,1</t>
+          <t>27,5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21,3</t>
+          <t>21,4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>26,7</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19,2</t>
+          <t>15,9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19,9</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>23,1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>32,3</t>
+          <t>32,8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22,7</t>
+          <t>20,7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25,7</t>
+          <t>24,6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>26,3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27,1</t>
+          <t>22,8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17,9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>23,8</t>
+          <t>18,8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -600,12 +600,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16,2</t>
+          <t>19,9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>23,5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>24,5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>24,2</t>
+          <t>23,3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>16,8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15,4</t>
+          <t>13,5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22,4</t>
+          <t>20,6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>23,8</t>
+          <t>25,2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>18,5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>26,5</t>
+          <t>22,2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22,9</t>
+          <t>22,3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>22,6</t>
+          <t>21,2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -904,12 +904,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15,5</t>
+          <t>18,6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>24,6</t>
+          <t>18,8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>23,2</t>
+          <t>22,3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -970,12 +970,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>26,2</t>
+          <t>23,2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>27,9</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>22,1</t>
+          <t>22,8</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27,5</t>
+          <t>17,5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>19,4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>26,1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15,9</t>
+          <t>17,8</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>20,2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>23,1</t>
+          <t>21,1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>32,8</t>
+          <t>31,8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -495,12 +495,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -512,12 +512,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26,3</t>
+          <t>24,7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22,8</t>
+          <t>18,1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17,9</t>
+          <t>19,2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18,8</t>
+          <t>23,4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>20,6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19,9</t>
+          <t>19,3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>21,3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24,5</t>
+          <t>23,7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23,3</t>
+          <t>23,4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -710,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16,8</t>
+          <t>21,7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13,5</t>
+          <t>14,6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20,6</t>
+          <t>21,4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>25,2</t>
+          <t>24,2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -799,12 +799,12 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18,5</t>
+          <t>18,9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22,2</t>
+          <t>21,7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22,3</t>
+          <t>23,1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21,2</t>
+          <t>23,2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18,6</t>
+          <t>18,4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18,8</t>
+          <t>20,5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>22,3</t>
+          <t>23,8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>23,2</t>
+          <t>21,7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>27,4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>22,8</t>
+          <t>20,2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17,5</t>
+          <t>21,4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19,4</t>
+          <t>19,5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>26,1</t>
+          <t>25,4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17,8</t>
+          <t>18,1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20,2</t>
+          <t>19,9</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21,1</t>
+          <t>20,1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31,8</t>
+          <t>29,1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24,6</t>
+          <t>22,1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24,7</t>
+          <t>16,4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18,1</t>
+          <t>19,6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19,2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>23,4</t>
+          <t>19,8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20,6</t>
+          <t>21,7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19,3</t>
+          <t>19,4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21,3</t>
+          <t>21,9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23,7</t>
+          <t>19,8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23,4</t>
+          <t>21,4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -710,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>19,4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14,6</t>
+          <t>14,4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>20,3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24,2</t>
+          <t>21,3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18,9</t>
+          <t>19,8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>16,8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>23,1</t>
+          <t>21,5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>23,2</t>
+          <t>21,5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18,4</t>
+          <t>18,2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20,5</t>
+          <t>22,4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>23,8</t>
+          <t>19,3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>16,2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>27,4</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20,2</t>
+          <t>13,1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>21,1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19,5</t>
+          <t>19,6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>25,4</t>
+          <t>24,8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18,1</t>
+          <t>18,3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19,9</t>
+          <t>19,4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20,1</t>
+          <t>18,6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29,1</t>
+          <t>23,4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>16,8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22,1</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>21,5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -534,12 +534,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19,6</t>
+          <t>14,5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14,5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19,8</t>
+          <t>19,3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21,7</t>
+          <t>12,3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19,4</t>
+          <t>11,4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21,9</t>
+          <t>17,8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19,8</t>
+          <t>19,4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>20,4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14,4</t>
+          <t>13,6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>17,2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21,3</t>
+          <t>22,9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -799,12 +799,12 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -816,17 +816,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19,8</t>
+          <t>12,6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16,8</t>
+          <t>20,7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21,5</t>
+          <t>19,9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21,5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18,2</t>
+          <t>10,9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>22,4</t>
+          <t>15,5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19,3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16,2</t>
+          <t>17,8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>21,6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13,1</t>
+          <t>15,2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21,1</t>
+          <t>16,6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19,6</t>
+          <t>19,7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>24,9</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18,3</t>
+          <t>11,5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19,4</t>
+          <t>23,2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18,6</t>
+          <t>15,8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23,4</t>
+          <t>19,6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16,8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22,5</t>
+          <t>17,9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21,5</t>
+          <t>13,5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14,5</t>
+          <t>14,3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14,5</t>
+          <t>18,6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19,3</t>
+          <t>15,4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12,3</t>
+          <t>18,4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11,4</t>
+          <t>14,8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17,8</t>
+          <t>17,4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19,4</t>
+          <t>13,4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20,4</t>
+          <t>16,3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19,4</t>
+          <t>17,9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13,6</t>
+          <t>10,2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17,2</t>
+          <t>18,3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22,9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -799,12 +799,12 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12,6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>15,4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19,9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17,3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10,9</t>
+          <t>14,4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15,5</t>
+          <t>18,3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13,5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17,8</t>
+          <t>13,2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21,6</t>
+          <t>23,1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15,2</t>
+          <t>11,4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16,6</t>
+          <t>18,4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1058,17 +1058,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19,7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>24,9</t>
+          <t>18,7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11,5</t>
+          <t>15,9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>23,2</t>
+          <t>19,8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15,8</t>
+          <t>14,7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19,6</t>
+          <t>17,3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14,4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17,9</t>
+          <t>16,3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13,5</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14,3</t>
+          <t>16,8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18,6</t>
+          <t>15,4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -578,12 +578,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15,4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14,8</t>
+          <t>15,9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17,4</t>
+          <t>16,4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -666,12 +666,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13,4</t>
+          <t>15,8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16,3</t>
+          <t>16,5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17,9</t>
+          <t>16,8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10,2</t>
+          <t>11,5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18,3</t>
+          <t>14,3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15,2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17,9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -838,17 +838,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15,4</t>
+          <t>19,7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12,3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17,3</t>
+          <t>15,2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -904,17 +904,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14,4</t>
+          <t>12,5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18,3</t>
+          <t>17,8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13,5</t>
+          <t>12,5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13,2</t>
+          <t>18,1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>23,1</t>
+          <t>16,3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11,4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18,4</t>
+          <t>17,5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>19,2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1080,17 +1080,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18,7</t>
+          <t>18,2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15,9</t>
+          <t>14,7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19,8</t>
+          <t>20,8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14,7</t>
+          <t>15,3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17,3</t>
+          <t>22,1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14,4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16,3</t>
+          <t>21,4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -512,12 +512,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23,7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16,8</t>
+          <t>16,2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15,4</t>
+          <t>12,9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18,4</t>
+          <t>15,9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15,9</t>
+          <t>15,3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>16,7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15,8</t>
+          <t>19,2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16,5</t>
+          <t>15,1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -710,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16,8</t>
+          <t>14,3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11,5</t>
+          <t>7,8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14,3</t>
+          <t>15,2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15,2</t>
+          <t>15,7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -796,10 +796,14 @@
           <t>HATAY</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20,4</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -816,17 +820,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17,9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -838,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19,7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -848,7 +852,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -860,12 +864,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12,3</t>
+          <t>13,5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -882,12 +886,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15,2</t>
+          <t>18,3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -904,12 +908,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12,5</t>
+          <t>13,3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -926,17 +930,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17,8</t>
+          <t>14,4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -948,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12,5</t>
+          <t>15,6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -970,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18,1</t>
+          <t>20,9</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -992,17 +996,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16,3</t>
+          <t>21,9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17,9</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1040,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17,5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1062,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19,2</t>
+          <t>17,7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1080,7 +1084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18,2</t>
+          <t>18,4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1090,7 +1094,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1102,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14,7</t>
+          <t>15,5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1128,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20,8</t>
+          <t>19,7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1146,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15,3</t>
+          <t>17,9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>

--- a/weather.xlsx
+++ b/weather.xlsx
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22,1</t>
+          <t>23,7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15,2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21,4</t>
+          <t>21,6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23,7</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -534,12 +534,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16,2</t>
+          <t>18,8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12,9</t>
+          <t>14,7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -578,12 +578,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13,8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15,9</t>
+          <t>17,9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15,3</t>
+          <t>16,4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16,7</t>
+          <t>15,4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19,2</t>
+          <t>19,3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15,1</t>
+          <t>16,2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -710,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14,3</t>
+          <t>14,9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7,8</t>
+          <t>9,7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15,2</t>
+          <t>17,7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15,7</t>
+          <t>16,1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20,4</t>
+          <t>20,8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15,4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19,7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13,5</t>
+          <t>16,9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -886,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18,3</t>
+          <t>15,7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -908,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13,3</t>
+          <t>16,2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14,4</t>
+          <t>15,5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15,6</t>
+          <t>16,8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20,9</t>
+          <t>20,2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21,9</t>
+          <t>22,6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17,9</t>
+          <t>15,5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1040,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16,3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1062,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17,7</t>
+          <t>16,7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18,4</t>
+          <t>19,2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15,5</t>
+          <t>16,7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19,7</t>
+          <t>18,2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17,9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
     </row>
